--- a/outputs/59129.xlsx
+++ b/outputs/59129.xlsx
@@ -195,40 +195,44 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="20" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,377 +489,377 @@
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="n">
+      <c r="E1" s="4" t="n">
         <v>42370</v>
       </c>
-      <c r="F1" s="3" t="n">
+      <c r="F1" s="4" t="n">
         <v>42401</v>
       </c>
-      <c r="G1" s="3" t="n">
+      <c r="G1" s="4" t="n">
         <v>42430</v>
       </c>
-      <c r="H1" s="3" t="n">
+      <c r="H1" s="4" t="n">
         <v>42461</v>
       </c>
-      <c r="I1" s="3" t="n">
+      <c r="I1" s="4" t="n">
         <v>42491</v>
       </c>
-      <c r="J1" s="3" t="n">
+      <c r="J1" s="4" t="n">
         <v>42522</v>
       </c>
-      <c r="K1" s="3" t="n">
+      <c r="K1" s="4" t="n">
         <v>42552</v>
       </c>
-      <c r="L1" s="3" t="n">
+      <c r="L1" s="4" t="n">
         <v>42583</v>
       </c>
-      <c r="M1" s="3" t="n">
+      <c r="M1" s="4" t="n">
         <v>42614</v>
       </c>
-      <c r="N1" s="3" t="n">
+      <c r="N1" s="4" t="n">
         <v>42644</v>
       </c>
-      <c r="O1" s="3" t="n">
+      <c r="O1" s="4" t="n">
         <v>42675</v>
       </c>
-      <c r="P1" s="3" t="n">
+      <c r="P1" s="4" t="n">
         <v>42705</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>40514</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="6"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=E1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(E1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=F1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(F1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=G1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(G1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=H1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(H1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=I1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(I1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="J2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=J1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(J1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=K1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(K1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=L1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(L1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=M1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(M1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=N1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(N1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=O1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(O1,0))))</f>
-        <v>20</v>
-      </c>
-      <c r="P2" s="0" t="n">
-        <f aca="false">SUMPRODUCT(($A$2:$A$22&lt;=P1)*(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(P1,0))))</f>
+      <c r="E2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(E1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(E1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(F1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(F1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(G1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(G1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(H1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(H1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(I1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(I1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(J1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(J1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(K1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(K1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(L1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(L1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(M1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(M1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(N1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(N1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(O1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(O1,0))))</f>
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <f aca="false">SUMPRODUCT(--($A$2:$A$22&lt;=EOMONTH(P1,0))*--(($B$2:$B$22="")+($B$2:$B$22&gt;EOMONTH(P1,0))))</f>
         <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>40665</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="8"/>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;E1)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;F1)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;G1)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;H1)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;I1)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;J1)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;K1)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;L1)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;M1)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;N1)</f>
         <v>0</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;O1)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <f aca="false">COUNTIF($C$2:$C$22,"="&amp;P1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>40721</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="D4" s="0" t="s">
+      <c r="B4" s="6"/>
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="K4" s="8" t="n">
+      <c r="K4" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="O4" s="8" t="n">
+      <c r="O4" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="P4" s="9" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>40931</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="D5" s="0" t="s">
+      <c r="B5" s="8"/>
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">SUM(E2-E3)-E4</f>
         <v>-5</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <f aca="false">SUM(F2-F3)-F4</f>
         <v>-5</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <f aca="false">SUM(G2-G3)-G4</f>
         <v>-7</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">SUM(H2-H3)-H4</f>
         <v>-7</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <f aca="false">SUM(I2-I3)-I4</f>
         <v>-9</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <f aca="false">SUM(J2-J3)-J4</f>
         <v>-9</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <f aca="false">SUM(K2-K3)-K4</f>
         <v>-11</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <f aca="false">SUM(L2-L3)-L4</f>
         <v>-11</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <f aca="false">SUM(M2-M3)-M4</f>
         <v>-13</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <f aca="false">SUM(N2-N3)-N4</f>
         <v>-13</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <f aca="false">SUM(O2-O3)-O4</f>
         <v>-15</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <f aca="false">SUM(P2-P3)-P4</f>
         <v>-15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>41110</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>42370</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>41298</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>41437</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>41652</v>
       </c>
-      <c r="B9" s="7"/>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>41652</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>41786</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>41799</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>41884</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>41981</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>42100</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>42114</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>42142</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>42142</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>42156</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>42163</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>42226</v>
       </c>
-      <c r="B21" s="7"/>
+      <c r="B21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>42296</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
